--- a/data/availability/projects/sodic/villette.xlsx
+++ b/data/availability/projects/sodic/villette.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Villette</t>
+          <t>Live inventory for villette</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,256 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>V Residence</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29.18</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="H4" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Duplex</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="H5" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="H6" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +877,738 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>F-4C-32</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>V Residence</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Design: 1B</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>23126000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>P1-1321-31</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Design: 2 BED</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>29185000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P1-1325-33</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Design: 2 BED</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>30187000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Q1-1710-22</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 3</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Design: 3 BED</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>34196000</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R1-1716-23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 3</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Design: 3 BED</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>33486000</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Duplex</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>S1-1324-03</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 2</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Design: DUPLEX</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>54607000</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S2-1320-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 2</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Design: 3 BED</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>31926000</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>U1-1310-12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SKY CONDOS 2</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Design: 3 BED</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>33950000</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Villette-V Residence-4F-41</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>V Residence</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Design: 3B+N</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>48865000</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Villette-V Residence-4G-32</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>V Residence</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Design: 1B</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>22602000</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Villette-V Residence-5D-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>V Residence</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Design: 3B+N+F</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>46227000</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>villette</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Villette-V Residence-5G-44</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>V Residence</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Semi Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Design: 3B+N</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>51426000</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10% down payment over 8 years equal installments</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/availability/projects/sodic/villette.xlsx
+++ b/data/availability/projects/sodic/villette.xlsx
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,63 +966,6 @@
         </is>
       </c>
       <c r="M5" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>villette</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Finished</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Landscape &amp; City View</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Ready / 2027</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>5% down · 7–8 years equal installments</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>Available</t>
         </is>

--- a/data/availability/projects/sodic/villette.xlsx
+++ b/data/availability/projects/sodic/villette.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Live inventory for villette</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
